--- a/data toko.xlsx
+++ b/data toko.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fathi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9D39983-D95F-403D-8492-5811D12C463B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF3205D-152A-4756-9B80-2955D07F9F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AD760F8-2F1A-41C5-A81A-9A06C2F9460C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="212">
   <si>
     <t>BRANCH NAME</t>
   </si>
@@ -559,6 +559,117 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/XE2GC84UQSqsugdPA</t>
+  </si>
+  <si>
+    <t>grab</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1FGCGGN53EE</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1GPCZTFNBJN</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1HFDTVJD1JX</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JX6XVUC3VN</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1GPC2T7XVR2</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1G6DHCNCFG2</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JP5YEBUXA6</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1E7CGEKL3GN</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7UBLCNYTJA2RJ</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1WBKERGKJRE</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JB32LFKGGA</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7UCNFCGJTCZE2</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1WBKUHFMGJ2</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7TKG8BZEBDDTJ</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JB4BVPNXKE</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7TAR8J1BCCZDA</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1GZCKLYNFET</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1EX4ALT5GNE</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1GPC3DCMBEX</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1GZCKL6T2RT</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7UYMF5FWFM3GJ</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1WBKURP6TTJ</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T2AXAKJTWWTT</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7THRZJKVE4HC2</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T2AGNXR7E3TX</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JX6XVBU1HA</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1WBLDCBWJRN</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JP5XE3LBRX</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T2CTAVJ6AHVT</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1WBKGLAXUNJ</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7UCLYC1HEKTNN</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1FGCHWBBKLA</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1GZCKL6U2NE</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T1JX6XVJAYEA</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T2AXADCGLFRN</t>
+  </si>
+  <si>
+    <t>https://r.grab.com/g/2-2-6-C7T2DGCUNVAKGX</t>
   </si>
 </sst>
 </file>
@@ -669,7 +780,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -737,12 +848,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF356854"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -808,6 +945,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1125,13 +1280,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E0DD09C-051E-40D5-9FE2-A535ED85C975}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1156,8 +1311,11 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="129" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="129" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1182,8 +1340,11 @@
       <c r="H2" s="20">
         <v>6285966715459</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
@@ -1208,8 +1369,11 @@
       <c r="H3" s="21">
         <v>6281944219564</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="180" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="180" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1234,8 +1398,11 @@
       <c r="H4" s="20">
         <v>6287722724824</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="218.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="218.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
@@ -1260,8 +1427,11 @@
       <c r="H5" s="21">
         <v>6287722724827</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="180" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="180" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -1286,8 +1456,11 @@
       <c r="H6" s="20">
         <v>6281949873164</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
@@ -1312,8 +1485,11 @@
       <c r="H7" s="21">
         <v>6287700293365</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="114" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="114" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
@@ -1338,8 +1514,11 @@
       <c r="H8" s="20">
         <v>628175200141</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="159" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="159" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>34</v>
       </c>
@@ -1364,8 +1543,11 @@
       <c r="H9" s="21">
         <v>6281944214740</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>34</v>
       </c>
@@ -1390,8 +1572,11 @@
       <c r="H10" s="20">
         <v>6287722724809</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>50</v>
       </c>
@@ -1416,8 +1601,11 @@
       <c r="H11" s="21">
         <v>628175200136</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="25" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
@@ -1442,8 +1630,11 @@
       <c r="H12" s="20">
         <v>6281944210513</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>34</v>
       </c>
@@ -1468,8 +1659,11 @@
       <c r="H13" s="21">
         <v>6281944219566</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="25" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -1494,8 +1688,11 @@
       <c r="H14" s="20">
         <v>6287722724806</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="159" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="159" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>34</v>
       </c>
@@ -1520,8 +1717,11 @@
       <c r="H15" s="21">
         <v>628175200134</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
@@ -1546,8 +1746,11 @@
       <c r="H16" s="20">
         <v>6281913580778</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>34</v>
       </c>
@@ -1572,8 +1775,11 @@
       <c r="H17" s="21">
         <v>6281944215238</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -1598,8 +1804,11 @@
       <c r="H18" s="20">
         <v>6285966715453</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>8</v>
       </c>
@@ -1624,8 +1833,11 @@
       <c r="H19" s="21">
         <v>6287722724796</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="25" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
@@ -1650,8 +1862,11 @@
       <c r="H20" s="20">
         <v>6281944219563</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>8</v>
       </c>
@@ -1676,8 +1891,11 @@
       <c r="H21" s="21">
         <v>6287722724813</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="159" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="159" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
@@ -1702,8 +1920,11 @@
       <c r="H22" s="20">
         <v>87722724816</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="204" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="204" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>103</v>
       </c>
@@ -1728,8 +1949,11 @@
       <c r="H23" s="21">
         <v>6287722724834</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>103</v>
       </c>
@@ -1754,8 +1978,11 @@
       <c r="H24" s="20">
         <v>6287722724838</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="26" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>103</v>
       </c>
@@ -1780,8 +2007,11 @@
       <c r="H25" s="21">
         <v>6287722724833</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="114" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="114" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>103</v>
       </c>
@@ -1806,8 +2036,11 @@
       <c r="H26" s="20">
         <v>6287854020222</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="136.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>103</v>
       </c>
@@ -1832,8 +2065,11 @@
       <c r="H27" s="21">
         <v>6287722724832</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>103</v>
       </c>
@@ -1858,8 +2094,11 @@
       <c r="H28" s="20">
         <v>6287722724837</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>103</v>
       </c>
@@ -1884,8 +2123,11 @@
       <c r="H29" s="21">
         <v>6287722724829</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>50</v>
       </c>
@@ -1910,8 +2152,11 @@
       <c r="H30" s="20">
         <v>628175200139</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="26" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="147.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
@@ -1936,8 +2181,11 @@
       <c r="H31" s="21">
         <v>628175200137</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="159" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="25" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="159" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>50</v>
       </c>
@@ -1962,8 +2210,11 @@
       <c r="H32" s="20">
         <v>628175200140</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="167.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="167.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>8</v>
       </c>
@@ -1988,8 +2239,11 @@
       <c r="H33" s="21">
         <v>6287722724795</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>8</v>
       </c>
@@ -2014,8 +2268,11 @@
       <c r="H34" s="20">
         <v>6287722724798</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>8</v>
       </c>
@@ -2040,8 +2297,11 @@
       <c r="H35" s="21">
         <v>6287700293366</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="204" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I35" s="25" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="204" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
@@ -2066,8 +2326,11 @@
       <c r="H36" s="20">
         <v>6281944220051</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="125.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>34</v>
       </c>
@@ -2092,8 +2355,11 @@
       <c r="H37" s="21">
         <v>6287722724805</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="170.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I37" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="170.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>34</v>
       </c>
@@ -2118,8 +2384,11 @@
       <c r="H38" s="22" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="170.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="170.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>170</v>
       </c>
@@ -2142,6 +2411,9 @@
         <v>174</v>
       </c>
       <c r="H39" s="19"/>
+      <c r="I39" s="28" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2183,8 +2455,44 @@
     <hyperlink ref="G37" r:id="rId36" xr:uid="{0BEE3DEC-5BD4-4AA5-81C5-9E1DD05347C7}"/>
     <hyperlink ref="G38" r:id="rId37" xr:uid="{9A42906C-81D1-41BF-951D-A65EEDF4DE47}"/>
     <hyperlink ref="G39" r:id="rId38" xr:uid="{81E54FFC-A1C4-4CEB-BD13-872811E4AD6D}"/>
+    <hyperlink ref="I2" r:id="rId39" xr:uid="{681C067D-244C-41DB-B51C-DC2C9FF08D63}"/>
+    <hyperlink ref="I3" r:id="rId40" xr:uid="{F15EB13E-9020-42B3-8E0A-7C89D28AF300}"/>
+    <hyperlink ref="I4" r:id="rId41" xr:uid="{CB1469DE-C7B8-4645-99C6-831DF74BCD3E}"/>
+    <hyperlink ref="I5" r:id="rId42" xr:uid="{89449CE7-DC5E-4848-B187-63B1B5614B33}"/>
+    <hyperlink ref="I6" r:id="rId43" xr:uid="{F3DBCB58-1A35-4091-895C-772150B10C4D}"/>
+    <hyperlink ref="I7" r:id="rId44" xr:uid="{ECCE4086-DF59-425A-AEF8-836678D53187}"/>
+    <hyperlink ref="I8" r:id="rId45" xr:uid="{79984853-757A-4D4D-81C2-8D7981E8BED0}"/>
+    <hyperlink ref="I9" r:id="rId46" xr:uid="{D234E4FA-CB55-4FC4-9140-A0B8223C07A5}"/>
+    <hyperlink ref="I10" r:id="rId47" xr:uid="{42B92666-F30E-49F0-AF15-2CE453D513EA}"/>
+    <hyperlink ref="I11" r:id="rId48" xr:uid="{A15676DD-F9E6-4BCB-A15E-77D10A8E2B51}"/>
+    <hyperlink ref="I12" r:id="rId49" xr:uid="{62F1F23A-FA97-4737-B542-968DE091B220}"/>
+    <hyperlink ref="I13" r:id="rId50" xr:uid="{BA3814CD-8B79-4FA7-985E-07401E470DE6}"/>
+    <hyperlink ref="I14" r:id="rId51" xr:uid="{EBB3C969-CD2B-4A2A-A1AC-EAF2DFFBA56E}"/>
+    <hyperlink ref="I15" r:id="rId52" xr:uid="{09C05A69-715B-4648-B20D-DE98C7DE537A}"/>
+    <hyperlink ref="I16" r:id="rId53" xr:uid="{6B329966-62F3-49B2-85D6-99BE2CF9C18E}"/>
+    <hyperlink ref="I17" r:id="rId54" xr:uid="{991BEF57-8C83-4EF2-89D9-7E9A5B58135C}"/>
+    <hyperlink ref="I18" r:id="rId55" xr:uid="{1FDBFF72-68A0-4F86-A147-96C38600E10D}"/>
+    <hyperlink ref="I19" r:id="rId56" xr:uid="{A738E41D-E5E0-48A8-90DC-B8E17907A1D8}"/>
+    <hyperlink ref="I20" r:id="rId57" xr:uid="{5086CC57-2FEE-4305-B1A1-82DF75D8AA06}"/>
+    <hyperlink ref="I21" r:id="rId58" xr:uid="{72D97A27-5F8E-49AF-81B4-90A4E2600E25}"/>
+    <hyperlink ref="I22" r:id="rId59" xr:uid="{278DAED5-7A3E-4F63-9350-4CAE0D7A4E3F}"/>
+    <hyperlink ref="I23" r:id="rId60" xr:uid="{D986AFA2-8985-47ED-9297-2012AECE7CA5}"/>
+    <hyperlink ref="I24" r:id="rId61" xr:uid="{228876A2-2E68-4287-959F-31AEEC90C62A}"/>
+    <hyperlink ref="I25" r:id="rId62" xr:uid="{687F4778-FF50-475C-A258-EE193E89FF2C}"/>
+    <hyperlink ref="I26" r:id="rId63" xr:uid="{DF3456C8-D4B3-490A-A85C-5EC60256AF84}"/>
+    <hyperlink ref="I27" r:id="rId64" xr:uid="{AC9FF970-E363-4302-B4C3-32E485805037}"/>
+    <hyperlink ref="I28" r:id="rId65" xr:uid="{95CD6F92-97DF-4FB5-811B-7EE86A751A9C}"/>
+    <hyperlink ref="I29" r:id="rId66" xr:uid="{147461B5-0538-4387-89C2-5E176F34147D}"/>
+    <hyperlink ref="I30" r:id="rId67" xr:uid="{2088556C-166B-4998-A6D6-4D3BE16AEF95}"/>
+    <hyperlink ref="I31" r:id="rId68" xr:uid="{45593A66-5384-4065-BB46-67FE3070CDA0}"/>
+    <hyperlink ref="I32" r:id="rId69" xr:uid="{DD0C8693-17A8-4901-9C46-1E678000BBCB}"/>
+    <hyperlink ref="I33" r:id="rId70" xr:uid="{02D294FF-F20B-4DBA-9526-BC1395779EA9}"/>
+    <hyperlink ref="I34" r:id="rId71" xr:uid="{4B73432A-4CA0-4C83-B45C-20DCABDC6E11}"/>
+    <hyperlink ref="I35" r:id="rId72" xr:uid="{865323DF-83AF-4B05-9953-27DC6E41B4F8}"/>
+    <hyperlink ref="I36" r:id="rId73" xr:uid="{C3389DCC-2A88-408C-97F3-8C52E2309431}"/>
+    <hyperlink ref="I37" r:id="rId74" xr:uid="{80BB867F-FA5C-475A-899C-E56EC657E8A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId39"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId75"/>
 </worksheet>
 </file>